--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2018_aysen.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:45</t>
+    <t xml:space="preserve">2026-09-24 00:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -672,7 +672,7 @@
         <v>-0.05</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.09</v>
@@ -695,7 +695,7 @@
         <v>-0.06</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>-0.23</v>
@@ -715,10 +715,10 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.02</v>
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="F11" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.01</v>
